--- a/AAII_Financials/Quarterly/HRL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HRL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>HRL</t>
   </si>
@@ -656,529 +656,541 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46229</v>
+      </c>
+      <c r="E7" s="2">
         <v>46138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46047</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45956</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45774</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45683</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45501</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45410</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45319</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45228</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45137</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44955</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44864</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44682</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44591</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44402</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44311</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44129</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44038</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43856</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43765</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43674</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43583</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43492</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43401</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43219</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43128</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43037</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42946</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42764</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2961300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2972600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3027300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3185700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3032900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2898800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2988800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3138100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2898400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2887400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2996900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3198100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2963300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2977600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2971000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3283500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3034400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3096600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3044400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3454800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2863700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2606600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2461100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2420100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2381500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2422500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2384400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2501500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2290700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2344700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2360400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2524700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2359100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2330600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2331300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2492600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2207400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2187300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2280200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2627900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2489400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2452700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2557400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2735400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2544600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2411600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2513400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2616000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2408800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2381700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2486600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2682700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2465300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2486200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2475000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2717100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2528400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2543100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2505600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2876700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2440300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2130300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2011000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1962300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1959000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1945100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1916000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2007800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1857300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1875600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1872000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1991400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1904100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1837700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1829100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1981100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1755000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1700400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1727900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2029400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>472000</v>
+      </c>
+      <c r="E10" s="3">
         <v>519900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>470000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>450200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>488300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>487200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>475400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>522100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>489600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>505600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>510300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>515400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>498000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>491400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>496000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>566400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>506000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>553500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>538800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>578100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>423400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>476300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>450100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>457800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>422500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>477400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>468400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>493700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>433400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>469100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>488400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>533300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>455000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>492900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>502200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>511500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>452400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>486900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>552300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>598500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1233,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1232,11 +1245,11 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>35200</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1244,11 +1257,11 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>36100</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -1256,11 +1269,11 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3">
         <v>33700</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
@@ -1343,8 +1356,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1465,46 +1481,49 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E14" s="3">
         <v>76600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>92100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>16600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>25700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>30500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>23600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>10300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>37700</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1518,8 +1537,8 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1542,17 +1561,17 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AD14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1560,11 +1579,11 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>17300</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
@@ -1572,68 +1591,71 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3">
         <v>200</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
         <v>0</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>66400</v>
+      </c>
+      <c r="E15" s="3">
         <v>68800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>67100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>69400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>64700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>64000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>65900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>66400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>63700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>63600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>64100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>66000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>64100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>61700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1709,8 +1731,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1750,252 +1775,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2706200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2696100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2803500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2955600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2789800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2649300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2750900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2842000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2639200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2626600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2718300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2890900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2756300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2698700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2681500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2916300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2743400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2761800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2724700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3097100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2656200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2317200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2193100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2143400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2131900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2129000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2103900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2180500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2034000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2032400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2054100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2205100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2102500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2028800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2024700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2163200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1927700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1871300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1924900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2262200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>255100</v>
+      </c>
+      <c r="E18" s="3">
         <v>276500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>223800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>230100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>243100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>249600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>237900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>296100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>259200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>260700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>278700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>307200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>207000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>278900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>289500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>367200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>291000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>334800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>319700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>357700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>207500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>289400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>268000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>276700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>249600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>293500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>280500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>321000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>256700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>312300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>306300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>319600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>256600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>301800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>306600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>329400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>279700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>316000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>355300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>365700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2038,266 +2070,273 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-19600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>137100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-11200</v>
-      </c>
       <c r="H20" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="I20" s="3">
         <v>-10800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-17800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-20100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-16100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>14400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>10100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>8400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>11000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>17300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>10300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>15500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>13300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>11300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>8300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>4200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>2500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>289600</v>
+      </c>
+      <c r="E21" s="3">
         <v>364800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>310500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>162400</v>
       </c>
-      <c r="G21" s="3">
-        <v>318900</v>
-      </c>
       <c r="H21" s="3">
+        <v>330300</v>
+      </c>
+      <c r="I21" s="3">
         <v>324300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>321600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>382500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>330900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>339500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>358800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>373700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>280800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>357500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>370400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>446300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>370600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>398700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>387800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>433700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>275100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>352700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>336400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>343000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>314900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>340600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>343100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>369800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>305700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>364400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>353100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>368600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>307000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>345100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>349000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>368400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>313900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>350900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>389100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>403500</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E22" s="3">
         <v>19800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>19700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>19500</v>
       </c>
       <c r="H22" s="3">
         <v>19500</v>
@@ -2306,350 +2345,359 @@
         <v>19500</v>
       </c>
       <c r="J22" s="3">
+        <v>19500</v>
+      </c>
+      <c r="K22" s="3">
         <v>19400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18300</v>
-      </c>
-      <c r="N22" s="3">
-        <v>18400</v>
       </c>
       <c r="O22" s="3">
         <v>18400</v>
       </c>
       <c r="P22" s="3">
-        <v>18300</v>
+        <v>18400</v>
       </c>
       <c r="Q22" s="3">
         <v>18300</v>
       </c>
       <c r="R22" s="3">
+        <v>18300</v>
+      </c>
+      <c r="S22" s="3">
         <v>17600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>15600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>3500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>3600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>3100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>6300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>4700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>3600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>3100</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>3000</v>
       </c>
       <c r="AO22" s="3">
         <v>3000</v>
       </c>
       <c r="AP22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AQ22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E23" s="3">
         <v>206100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>234300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-21600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>236500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>230500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>218100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>280000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>225700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>244100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>285500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>245800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>207600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>278800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>281200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>357500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>289800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>321900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>308900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>352200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>204200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>292600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>277100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>278700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>259400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>286500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>290200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>323700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>261000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>318000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>307000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>321500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>257700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>296900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>305200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>330000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>278000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>315800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>354800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>364700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E24" s="3">
         <v>48700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>52500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>34600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>52800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>50700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>47500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>60100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>49000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>54900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>66800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>50300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>45100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>61600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>63600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>77500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>71000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>60200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>69200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>70500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>27200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>64700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>54700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>44200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>56100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>58900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>47200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>68100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>61600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>35400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>65500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>132900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>59400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>64800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>111600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>95500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>104900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>119500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>120500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2770,252 +2818,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E26" s="3">
         <v>157400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>181800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-56200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>183700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>179700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>170500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>220000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>176700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>189200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>218700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>195500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>162600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>217200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>217700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>280000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>218800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>261700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>239700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>281800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>177100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>227900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>222400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>234500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>203300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>227600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>243000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>255600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>199400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>282600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>241500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>188600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>210400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>237500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>240400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>218400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>182600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>210900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>235300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>244200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E27" s="3">
         <v>157500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>181800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-56100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>183700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>180000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>170600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>220200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>176700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>189300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>218900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>195900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>162700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>217200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>217700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>279900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>218900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>261600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>239600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>281700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>176900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>227900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>222300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>234400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>203100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>227700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>242900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>255500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>199400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>282400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>241400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>188500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>210200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>237400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>240300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>218200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>182500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>210900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>235100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>243900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3136,8 +3193,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3213,8 +3273,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3231,20 +3291,20 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>72900</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>5800</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>62800</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3258,8 +3318,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3380,8 +3443,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3502,252 +3568,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E32" s="3">
         <v>19500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>19600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-137100</v>
       </c>
-      <c r="G32" s="3">
-        <v>11200</v>
-      </c>
       <c r="H32" s="3">
+        <v>22500</v>
+      </c>
+      <c r="I32" s="3">
         <v>10800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>17800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>20100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>16100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>16900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-14400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-10100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-8400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-17300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-15500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-9500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E33" s="3">
         <v>157500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>181800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-56100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>183700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>180000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>170600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>220200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>176700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>189300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>218900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>195900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>162700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>217200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>217700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>279900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>218900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>261600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>239600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>281700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>176900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>227900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>222300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>234400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>203100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>227700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>242900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>255500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>199400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>282400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>241400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>261400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>221200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>243200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>303100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>218200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>182500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>210900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>235100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>243900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3868,257 +3943,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E35" s="3">
         <v>157500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>181800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-56100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>183700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>180000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>170600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>220200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>176700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>189300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>218900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>195900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>162700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>217200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>217700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>279900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>218900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>261600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>239600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>281700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>176900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>227900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>222300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>234400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>203100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>227700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>242900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>255500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>199400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>282400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>241400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>261400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>221200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>243200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>303100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>218200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>182500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>210900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>235100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>243900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46229</v>
+      </c>
+      <c r="E38" s="2">
         <v>46138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46047</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45956</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45774</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45683</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45501</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45410</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45319</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45228</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45137</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44955</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44864</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44682</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44591</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44402</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44311</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44129</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44038</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43856</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43765</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43674</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43583</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43492</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43401</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43219</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43128</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43037</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42946</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42764</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4161,8 +4245,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4205,222 +4290,226 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>839600</v>
+      </c>
+      <c r="E41" s="3">
         <v>826800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>867900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>670700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>599200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>669700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>840400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>741900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>537500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1486400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>963200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>736500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>669100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>580500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>599800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>982100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>850300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>861700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>824400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>613500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>291400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1484500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1751500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1714300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1729400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>606100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>724400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>672900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>560200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>639300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>512700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>459100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>269000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>261600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>385800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>444100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>633300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>548900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>609800</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>415100</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E42" s="3">
         <v>33100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>33300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>32900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>31500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>29300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>26000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>24700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>24500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>23100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>16700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>17400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>17500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>17800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>18300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>23500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>22200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>21200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>18400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>17700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>17500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>17300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>17600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>16800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>14800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>14700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>14100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>6700</v>
-      </c>
-      <c r="AG42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>8</v>
@@ -4431,8 +4520,8 @@
       <c r="AJ42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK42" s="3">
-        <v>0</v>
+      <c r="AK42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL42" s="3">
         <v>0</v>
@@ -4449,862 +4538,886 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>792100</v>
+      </c>
+      <c r="E43" s="3">
         <v>818800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>755100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>881600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>814900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>794500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>818600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>868300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>727100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>732000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>751000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>824600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>793700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>769100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>794400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>874800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>810600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>803100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>820400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>904000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>912400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>731400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>715700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>743900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>649600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>536400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>562700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>594300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>529300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>537700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>565200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>604400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>563800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>554300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>569300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>640700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>549000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>567300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>530900</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>609600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1801600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1750900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1647300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1747300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1821900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1729200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1516700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1576300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1649600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1673500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1578200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1680400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1737900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1745800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1730100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1716100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1679200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1597000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1385700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1369200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1426700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1229000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1086700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1072800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>982400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1049000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1057300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1042400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1108500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1030600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>994400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>963500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1001000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1011200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>973200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>921000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1013200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>988400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>958100</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>985700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E45" s="3">
         <v>15500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>9800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>53300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>48000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>45100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>88300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>40600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>51600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>30300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>30800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>30900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>40600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>35800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>37100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>33900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>28400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>23000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>20500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>23700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>20000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>20700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>21500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>21100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>20800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>19500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3526200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3493600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3388200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3405700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3322500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3282100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3266100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3246500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2997400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3976500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3367200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3297200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3254800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3162600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3195300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3637100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3403500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3373600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3093400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2947800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2688700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3514300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3601700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3579100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3409800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2248900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2395000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2361400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2246000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2250700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2100700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2050100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1854300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1850800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1948300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2026500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2217100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2125800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2119600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2029900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>527900</v>
+      </c>
+      <c r="E47" s="3">
         <v>568500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>577100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>534000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>698600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>682800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>710400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>719500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>680400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>710000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>728100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>725100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>743500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>742300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>701600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>271100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>277700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>275800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>286500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>299000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>304400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>309300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>304900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>308400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>298600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>303200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>290800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>289200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>279300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>276500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>277800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>273200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>276500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>265600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>262100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>242400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>248100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>246800</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>243900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>239600</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2163000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2166100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2241500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2402100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2212700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2191800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2174800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2342400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2168500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2163100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2155500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2297700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2131500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2119100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2124400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2141100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2118100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2123600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2101800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2181400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2067100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1897500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1898300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1951300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1855800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1809200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1755500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1629100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1516400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1494600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1483700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1512600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1410300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1353900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1293100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1203300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1054100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1043600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1035300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1105400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6440600</v>
+      </c>
+      <c r="E49" s="3">
         <v>6457600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6476600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6571400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6644700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6645400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6644500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6656200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6667300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6677800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6684400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6685600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6722400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6724500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6726700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6728900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6737600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6750300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6745300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6751400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6770800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3682400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3691000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3689000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3696200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3706800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3515900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3515500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3525400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3527000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3921700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3921300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3971500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3983300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3980800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3146800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2705400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2707400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2709500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2737800</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5425,8 +5538,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5547,130 +5663,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>634300</v>
+      </c>
+      <c r="E52" s="3">
         <v>658500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>633000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>480000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>618200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>619600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>607700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>470200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>600100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>607900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>577700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>443000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>574700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>567200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>535100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>528700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>603600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>598900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>600000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>516700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>501200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>485500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>462100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>380500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>340100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>327100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>333000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>313800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>387500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>387000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>371500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>385100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>382800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>376300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>374600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>356900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>283300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>262100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>258200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>257400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5791,130 +5913,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13292000</v>
+      </c>
+      <c r="E54" s="3">
         <v>13344300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13316400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13393100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13496700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13421800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13403500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13434700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13113800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14135400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13513000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13448800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13426800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13315700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13283000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13306900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13140400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13122300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12827000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12696300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12332200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9889000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9957900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9908300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9600500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8395200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8290100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8109000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7954600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7935700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8155400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8142300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7895400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7829700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>7858800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>6975900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>6508000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>6385700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>6366400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>6370100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5957,8 +6085,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6001,198 +6130,202 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>678000</v>
+      </c>
+      <c r="E57" s="3">
         <v>669400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>670900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>731600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>707800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>716900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>709200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>735600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>675200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>691500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>741900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>771400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>703400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>750300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>764500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>816600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>799200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>826700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>799400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>793300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>654200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>577400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>558500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>644600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>537500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>496500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>487700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>587200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>512100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>521700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>504300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>618800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>489000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>465600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>532800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>552700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>421200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>372400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>387700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>481800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>505600</v>
+      </c>
+      <c r="E58" s="3">
         <v>505300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>41400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>7200</v>
       </c>
       <c r="I58" s="3">
         <v>7200</v>
       </c>
       <c r="J58" s="3">
+        <v>7200</v>
+      </c>
+      <c r="K58" s="3">
         <v>39900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>957300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>954000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>976800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>947000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8900</v>
-      </c>
-      <c r="R58" s="3">
-        <v>8800</v>
       </c>
       <c r="S58" s="3">
         <v>8800</v>
       </c>
       <c r="T58" s="3">
+        <v>8800</v>
+      </c>
+      <c r="U58" s="3">
         <v>8100</v>
-      </c>
-      <c r="U58" s="3">
-        <v>8800</v>
       </c>
       <c r="V58" s="3">
         <v>8800</v>
       </c>
       <c r="W58" s="3">
+        <v>8800</v>
+      </c>
+      <c r="X58" s="3">
         <v>8700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9300</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>258700</v>
       </c>
       <c r="Z58" s="3">
         <v>258700</v>
@@ -6201,13 +6334,13 @@
         <v>258700</v>
       </c>
       <c r="AB58" s="3">
+        <v>258700</v>
+      </c>
+      <c r="AC58" s="3">
         <v>258300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8300</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
@@ -6215,23 +6348,23 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH58" s="3">
         <v>374900</v>
       </c>
-      <c r="AH58" s="3" t="s">
+      <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>95000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>185000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>255000</v>
-      </c>
-      <c r="AL58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM58" s="3" t="s">
         <v>8</v>
@@ -6242,338 +6375,347 @@
       <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AP58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>53600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>87800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>47400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>599900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>647900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>611900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>645800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>607100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>613600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>588300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>588500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>600700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>630800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>569800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>527100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>517800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>560900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>530000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>556700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>520100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>512900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>497900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>535700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>505500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>456600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>452200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>532100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>571400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1874000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1802800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1272900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1380800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1345500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1327700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1331800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1399300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1309700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2304800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2260800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2311800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2320600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1305200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1373400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1473300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1419900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1480700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1415300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1415700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1251200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1175200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1417500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1504000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1427100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1324600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1023100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1105000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1073100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1051700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1435800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1138900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1096800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1148500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1323500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1058200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>877800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>824600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>919800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1053200</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2349500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2351000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2851000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2984000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2850200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2850700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2850200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2972200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2851600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2852600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2357200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2468000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2360400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3294400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3292600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3290500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3294300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3294100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3309200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3315100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3316300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1040500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1043100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1044900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1046800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>56900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>309000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>250000</v>
       </c>
       <c r="AE61" s="3">
         <v>250000</v>
@@ -6585,7 +6727,7 @@
         <v>250000</v>
       </c>
       <c r="AH61" s="3">
-        <v>624800</v>
+        <v>250000</v>
       </c>
       <c r="AI61" s="3">
         <v>624800</v>
@@ -6594,10 +6736,10 @@
         <v>624800</v>
       </c>
       <c r="AK61" s="3">
+        <v>624800</v>
+      </c>
+      <c r="AL61" s="3">
         <v>624700</v>
-      </c>
-      <c r="AL61" s="3">
-        <v>250000</v>
       </c>
       <c r="AM61" s="3">
         <v>250000</v>
@@ -6611,130 +6753,136 @@
       <c r="AP61" s="3">
         <v>250000</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>250000</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>204300</v>
+      </c>
+      <c r="E62" s="3">
         <v>215600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>219300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>92100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>226300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>222300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>206200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>89900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>217000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>220600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>193200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>82700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>163800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>165400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>998100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1002900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1059300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1002300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>996200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>987200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>971000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>967500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>941700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>929100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>854900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>847500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>862000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>828400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>740200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>732300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>763800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>773700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>778000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>764900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>755200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>728000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>627000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>624700</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>621300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>615500</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6855,8 +7003,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6977,8 +7128,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7099,130 +7253,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5432400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5380400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5363200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5477300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5403600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5379900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5365000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5430700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5236600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6238900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5664400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5709800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5708900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5624100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5669100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5771600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5778700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5782900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5726400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5723400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5543900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3188300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3407400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3482700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3333000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2233100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2198300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2187500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2067500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2038400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2453700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2541500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2503800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2542500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2707500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2040000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1758300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1702600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1794400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1922100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7265,8 +7425,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7387,8 +7548,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7509,8 +7673,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7631,8 +7798,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7753,130 +7923,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7431800</v>
+      </c>
+      <c r="E72" s="3">
         <v>7533600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7537500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7516700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7732600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7708700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7688700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7677500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7612600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7591200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7557200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7493000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7447600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7435300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7380700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7313400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7177000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7100700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6980500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6881900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6743700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6699300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6604500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6523300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6414800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6336900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6246600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6128200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5984300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6003600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5856000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5730000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5615100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5504200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5366500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5162600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5033900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4974500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4866400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4736600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7997,8 +8173,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8119,8 +8298,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8241,130 +8423,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7843400</v>
+      </c>
+      <c r="E76" s="3">
         <v>7949300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7938500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7901200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8083300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8032300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8028300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7993400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7867100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7886000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7844100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7734900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7713300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7686500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7613900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7535300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7361700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7339400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7100600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6972900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6788300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6700700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6550500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6425500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6267400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6162100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6091800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5921500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5887100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5897300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5701700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5600800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5391600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5287200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5151300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4935900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4749700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4683100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4572000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4448000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8485,257 +8673,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46229</v>
+      </c>
+      <c r="E80" s="2">
         <v>46138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46047</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45956</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45774</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45683</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45501</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45410</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45319</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45228</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45137</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44955</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44864</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44682</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44591</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44402</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44311</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44129</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44038</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43856</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43765</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43674</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43583</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43492</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43401</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43310</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43219</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43128</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43037</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42946</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42764</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42673</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E81" s="3">
         <v>157500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>181800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-56100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>183700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>180000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>170600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>220200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>176700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>189300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>218900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>195900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>162700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>217200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>217700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>279900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>218900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>261600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>239600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>281700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>176900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>227900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>222300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>234400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>203100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>227700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>242900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>255500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>199400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>282400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>241400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>261400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>221200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>243200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>303100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>218200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>182500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>210900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>235100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>243900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8778,130 +8975,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E83" s="3">
         <v>60400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>62000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>54900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>59700</v>
       </c>
       <c r="H83" s="3">
         <v>59700</v>
       </c>
       <c r="I83" s="3">
+        <v>59700</v>
+      </c>
+      <c r="J83" s="3">
         <v>59600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>53800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>59500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>57100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>56900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>21500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>65100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>57300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>70900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>71200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>65100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>62200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>64300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>65900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>59200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>52300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>51000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>56000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>49900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>50600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>49300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>43000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>40700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>40000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>40800</v>
       </c>
       <c r="AI83" s="3">
         <v>40800</v>
       </c>
       <c r="AJ83" s="3">
+        <v>40800</v>
+      </c>
+      <c r="AK83" s="3">
         <v>41200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>39100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>34900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>32800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>32000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>31300</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>35400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9022,8 +9223,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9144,8 +9348,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9266,8 +9473,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9388,8 +9598,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9510,130 +9723,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>240600</v>
+      </c>
+      <c r="E89" s="3">
         <v>178900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>349200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>322900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>156700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>56400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>309200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>408600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>218000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>236100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>404000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>319100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>317000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>208100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>203600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>371800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>186000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>193400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>383800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>564100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>76500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>155600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>205700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>249900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>329800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>359900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>188400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>350100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>207300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>178200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>187400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>498500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>299900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>139200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>304200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>502500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>250800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>85300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>195200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>371200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9676,130 +9895,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-68200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-82200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-69000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-91500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-72200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-75100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-72200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-83800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-65500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-60000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-47200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-101700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-77900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-53500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-37100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-89700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-61000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-78500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-49700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-93100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-53800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-45200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-40400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-140700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-88300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-80400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-58200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-139600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-66600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-48200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-39400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-145600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-102800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-87500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-53700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-102800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-41500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-78200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-75800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-89700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9920,8 +10143,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10042,130 +10268,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-61500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-58700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-93600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-66300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-78300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-60300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-60000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-64200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-64600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-48200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-101100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-77400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-59600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-451500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-86200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-46000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-76100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-49700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-95500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3443100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-48000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-39300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-150300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-82900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-362600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-60500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-134800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-69900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>426500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-139400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-109500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-81200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-905300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-610900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-40400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-41500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>105600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-81100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10208,16 +10440,17 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E96" s="3">
         <v>160900</v>
-      </c>
-      <c r="E96" s="3">
-        <v>159500</v>
       </c>
       <c r="F96" s="3">
         <v>159500</v>
@@ -10226,112 +10459,115 @@
         <v>159500</v>
       </c>
       <c r="H96" s="3">
+        <v>159500</v>
+      </c>
+      <c r="I96" s="3">
         <v>159200</v>
-      </c>
-      <c r="I96" s="3">
-        <v>155000</v>
       </c>
       <c r="J96" s="3">
         <v>155000</v>
       </c>
       <c r="K96" s="3">
+        <v>155000</v>
+      </c>
+      <c r="L96" s="3">
         <v>154900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>154700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>150300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>150400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>149900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>150600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-142000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-141900</v>
       </c>
       <c r="S96" s="3">
         <v>-141900</v>
       </c>
       <c r="T96" s="3">
+        <v>-141900</v>
+      </c>
+      <c r="U96" s="3">
         <v>-141200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-132900</v>
       </c>
       <c r="V96" s="3">
         <v>-132900</v>
       </c>
       <c r="W96" s="3">
+        <v>-132900</v>
+      </c>
+      <c r="X96" s="3">
         <v>-132400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-132300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-125500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-125400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-125300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-124500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-112100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-112700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-112200</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-100100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-99600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-99400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-99300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-89800</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-89700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-89800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-89900</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-76600</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-76700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10452,8 +10688,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10574,8 +10813,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10696,8 +10938,11 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10705,361 +10950,370 @@
         <v>-163000</v>
       </c>
       <c r="E100" s="3">
+        <v>-163000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-162400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-158100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-163300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-149600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-143100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-150300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1100900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>354400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-133400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-149100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-144200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-165200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-141600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-142200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-140500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-80000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-124000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-143400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2172400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-373700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-134800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-117800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>872700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-110800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-77900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-100300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-215500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-481600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-128900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-165600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-178600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-182300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>538200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-77600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-125100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-104300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-82200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-253300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>7100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-10900</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>7100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-10900</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3500</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>-3300</v>
       </c>
       <c r="AH101" s="3">
         <v>-3300</v>
       </c>
       <c r="AI101" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>4600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>3200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-6300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-41200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>197200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>71500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-70500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-170700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>98500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>204400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-948900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>523200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>226700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>67400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>88600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-382300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>131800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>37300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>210900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>322200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1193200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-267000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>37200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1123300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-118300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>51500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>112700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-79100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>126600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>53600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>190200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-124200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-58300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-189200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>84400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-60900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>194700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>35500</v>
       </c>
     </row>
